--- a/datapackages/sisor/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/datapackages/sisor/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -8597,7 +8597,7 @@
         <v>150000</v>
       </c>
       <c r="R120" t="n">
-        <v>20000000</v>
+        <v>19850000</v>
       </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>

--- a/datapackages/sisor/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/datapackages/sisor/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -8034,7 +8034,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO'S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
+          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO`S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -15916,7 +15916,7 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG'S</t>
+          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">

--- a/datapackages/sisor/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/datapackages/sisor/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X301"/>
+  <dimension ref="A1:X302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,19 +804,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1251</v>
+        <v>1091</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>302</v>
+        <v>62</v>
       </c>
       <c r="D6" t="n">
-        <v>135</v>
+        <v>714</v>
       </c>
       <c r="E6" t="n">
-        <v>2060</v>
+        <v>1064</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -827,12 +827,10 @@
       <c r="H6" t="n">
         <v>5</v>
       </c>
-      <c r="I6" t="n">
-        <v>12876</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Adequação da estrutura física do NAIS/9ª RPM, visando ao atendimento dos requisitos necessários à regularização junto aos órgãos de controle, especialmente à Vigilância Sanitária e à Secretaria de Saúde</t>
+          <t>Sedes Próprias Diversas</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -840,31 +838,25 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>60000</v>
+        <v>19960975</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -902,11 +894,11 @@
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>12882</v>
+        <v>12876</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Projeto elétrico, hidráulico, esgoto, rede, serralheria (prateleiras) e arquitetônico para reforma do CAO/CODONT; Valor estimado: R$ 197.856,73.</t>
+          <t>Adequação da estrutura física do NAIS/9ª RPM, visando ao atendimento dos requisitos necessários à regularização junto aos órgãos de controle, especialmente à Vigilância Sanitária e à Secretaria de Saúde</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -929,16 +921,16 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>197857</v>
+        <v>60000</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -976,11 +968,11 @@
         <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>12880</v>
+        <v>12882</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Projeto de reestruturação dos consultórios de roseta para linha;</t>
+          <t xml:space="preserve"> Projeto elétrico, hidráulico, esgoto, rede, serralheria (prateleiras) e arquitetônico para reforma do CAO/CODONT; Valor estimado: R$ 197.856,73.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1012,7 +1004,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>1929103</v>
+        <v>197857</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1050,11 +1042,11 @@
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>12881</v>
+        <v>12880</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Execução das obras de reestruturação dos consultórios de roseta para linha;</t>
+          <t xml:space="preserve"> Projeto de reestruturação dos consultórios de roseta para linha;</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1124,11 +1116,11 @@
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>12878</v>
+        <v>12881</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Contratação de elaboração de estudo e projeto para adaptação do NAIS/5GRS, em atendimento às normas de vigilância sanitária para coleta de resíduos sólidos médico-hospitalares e construção de vestiários.</t>
+          <t>Execução das obras de reestruturação dos consultórios de roseta para linha;</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1151,16 +1143,16 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Região Intermediária de Governador Valadares</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>GOVERNADOR VALADARES</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>41022</v>
+        <v>1929103</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1198,11 +1190,11 @@
         <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>12875</v>
+        <v>12878</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Construlção de local adequado para o armazenamento e descarte de resíduos de serviços de saúde, sendo necessária a adequação da estrutura física para atendimento às exigências dos órgãos de controle e consequente obtenção do alvará sanitário.</t>
+          <t>Contratação de elaboração de estudo e projeto para adaptação do NAIS/5GRS, em atendimento às normas de vigilância sanitária para coleta de resíduos sólidos médico-hospitalares e construção de vestiários.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1225,16 +1217,16 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Governador Valadares</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DIAMANTINA</t>
+          <t>GOVERNADOR VALADARES</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>100000</v>
+        <v>41022</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1248,33 +1240,35 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>368</v>
+        <v>302</v>
       </c>
       <c r="D12" t="n">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="E12" t="n">
-        <v>4519</v>
+        <v>2060</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>11</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>12875</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORÇO ESTRUTURAL, REFORMA E AMPLIAÇÃO - EE ABRE CAMPO</t>
+          <t>Construlção de local adequado para o armazenamento e descarte de resíduos de serviços de saúde, sendo necessária a adequação da estrutura física para atendimento às exigências dos órgãos de controle e consequente obtenção do alvará sanitário.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1282,7 +1276,11 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
@@ -1293,16 +1291,16 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ABRE CAMPO</t>
+          <t>DIAMANTINA</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380000</v>
+        <v>100000</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1342,7 +1340,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>OBRA DE COMBATE A INCÊNDIO DE TODO O COMPLEXO E ACESSIBILIDADE NO CAMPUS GAMELEIRA - PRÉDIOS A,B,C,D (INCLUNDO MUSEU ESCOLA ANA MARIA CASASANTA PEIXOTO E MUSEU LEOPOLDO CATHOUD) E EE LEON RENAULT</t>
+          <t>OBRA PARA REFORÇO ESTRUTURAL, REFORMA E AMPLIAÇÃO - EE ABRE CAMPO</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1361,16 +1359,16 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ABRE CAMPO</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>653600</v>
+        <v>380000</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1410,7 +1408,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE GETÚLIO VARGAS</t>
+          <t>OBRA DE COMBATE A INCÊNDIO DE TODO O COMPLEXO E ACESSIBILIDADE NO CAMPUS GAMELEIRA - PRÉDIOS A,B,C,D (INCLUNDO MUSEU ESCOLA ANA MARIA CASASANTA PEIXOTO E MUSEU LEOPOLDO CATHOUD) E EE LEON RENAULT</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1438,7 +1436,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>332120</v>
+        <v>653600</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1478,7 +1476,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE JOSÉ BONIFÁCIO</t>
+          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE GETÚLIO VARGAS</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1506,7 +1504,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>1033600</v>
+        <v>332120</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1546,7 +1544,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PROJETOS EXECUTIVOS PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
+          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE JOSÉ BONIFÁCIO</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1574,7 +1572,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>59660</v>
+        <v>1033600</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1614,7 +1612,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
+          <t>PROJETOS EXECUTIVOS PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1642,7 +1640,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>83600</v>
+        <v>59660</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1682,7 +1680,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>OBRAS DE REFORMA GERAL EE PROF CAETANO AZEREDO</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1710,7 +1708,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805600</v>
+        <v>83600</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1750,7 +1748,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>OBRA PARA REGULARIZAÇÃO DO PROCESSO DE SEGURANÇA CONTRA INCÊNDIO E PÂNICO (PSCIP), ADEQUAÇÃO À ACESSIBILIDADE EE PEDRO II</t>
+          <t>OBRAS DE REFORMA GERAL EE PROF CAETANO AZEREDO</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1778,7 +1776,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387600</v>
+        <v>805600</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -1818,7 +1816,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO (SOLUÇÃO DE PROBLEMAS ESTRUTURAIS) EE SANDOVAL AZEVEDO</t>
+          <t>OBRA PARA REGULARIZAÇÃO DO PROCESSO DE SEGURANÇA CONTRA INCÊNDIO E PÂNICO (PSCIP), ADEQUAÇÃO À ACESSIBILIDADE EE PEDRO II</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1846,7 +1844,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>251560</v>
+        <v>387600</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -1886,7 +1884,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA GERAL/RESTAURAÇÃO (MENOS TELHADO DA CASA MODELO, MURO DE ARRIMO) EE SÃO RAFAEL</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO (SOLUÇÃO DE PROBLEMAS ESTRUTURAIS) EE SANDOVAL AZEVEDO</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1914,7 +1912,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>2121920</v>
+        <v>251560</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -1954,7 +1952,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA - ESTRUTURA ESCOLA GUIGNARD UEMG</t>
+          <t>OBRA DE REFORMA GERAL/RESTAURAÇÃO (MENOS TELHADO DA CASA MODELO, MURO DE ARRIMO) EE SÃO RAFAEL</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1982,7 +1980,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>1929640</v>
+        <v>2121920</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2022,12 +2020,12 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>OBRAS DE REFORMA E RESTAURAÇÃO DOS PRÉDIOS INSTITUTO DE EDUCAÇÃO DE MINAS GERAIS - IEMG</t>
+          <t>OBRA DE REFORMA - ESTRUTURA ESCOLA GUIGNARD UEMG</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -2050,7 +2048,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>3040000</v>
+        <v>1929640</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2090,12 +2088,12 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA, DO PRÉDIO DO ANTIGO AUDITÓRIO DO CAMPUS DA SEE-  GAMELEIRA, PARA ABRIGAR A NOVA SEDE DA SRE MET B - SEDE DA SRE MET B - AUDITÓRIO GAMELEIRA</t>
+          <t>OBRAS DE REFORMA E RESTAURAÇÃO DOS PRÉDIOS INSTITUTO DE EDUCAÇÃO DE MINAS GERAIS - IEMG</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -2118,7 +2116,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>3025160</v>
+        <v>3040000</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2158,7 +2156,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>OBRA  PARA REFORMA/RESTAURAÇÃO EE SÃO JOAQUIM</t>
+          <t>OBRA PARA REFORMA, DO PRÉDIO DO ANTIGO AUDITÓRIO DO CAMPUS DA SEE-  GAMELEIRA, PARA ABRIGAR A NOVA SEDE DA SRE MET B - SEDE DA SRE MET B - AUDITÓRIO GAMELEIRA</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2182,11 +2180,11 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CONCEIÇÃO DO MATO DENTRO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>2105200</v>
+        <v>3025160</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2226,12 +2224,12 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>OBRA DE ESTRUTURA E OUTRAS, EM PRÉDIO TOMBADO</t>
+          <t>OBRA  PARA REFORMA/RESTAURAÇÃO EE SÃO JOAQUIM</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -2250,11 +2248,11 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CORDISBURGO</t>
+          <t>CONCEIÇÃO DO MATO DENTRO</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>260300</v>
+        <v>2105200</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2294,12 +2292,12 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E SOLUÇÃO DE PROBLEMAS ESTRUTURAIS EE ODILON BEHRENS</t>
+          <t>OBRA DE ESTRUTURA E OUTRAS, EM PRÉDIO TOMBADO</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -2313,16 +2311,16 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Região Intermediária de Governador Valadares</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>GUANHÃES</t>
+          <t>CORDISBURGO</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>1705060</v>
+        <v>260300</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -2362,7 +2360,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> OBRA PARA SOLUÇÃO DE DESLIZAMENTO DE TERRA DE PARTE DO TALUDE E A RUPTURA DE PARTE DO MURO DIVISÓRIO INTERNO EE SELIM JOSÉ DE SALES</t>
+          <t>OBRA PARA REFORMA E SOLUÇÃO DE PROBLEMAS ESTRUTURAIS EE ODILON BEHRENS</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2381,16 +2379,16 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Governador Valadares</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>IPATINGA</t>
+          <t>GUANHÃES</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>190000</v>
+        <v>1705060</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2430,7 +2428,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>OBRAS PARA RESTAURAÇÃO DO PRÉDIO EE WENCESLAU BRAZ</t>
+          <t xml:space="preserve"> OBRA PARA SOLUÇÃO DE DESLIZAMENTO DE TERRA DE PARTE DO TALUDE E A RUPTURA DE PARTE DO MURO DIVISÓRIO INTERNO EE SELIM JOSÉ DE SALES</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2449,16 +2447,16 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>ITAJUBÁ</t>
+          <t>IPATINGA</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>2420600</v>
+        <v>190000</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2498,7 +2496,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E CONTENÇÃO E ESTABILIDADE DE TALUDE E DO PRÉDIO EE SÃO JOSÉ</t>
+          <t>OBRAS PARA RESTAURAÇÃO DO PRÉDIO EE WENCESLAU BRAZ</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2517,16 +2515,16 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>ALÉM PARAÍBA</t>
+          <t>ITAJUBÁ</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691600</v>
+        <v>2420600</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2566,7 +2564,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE RAUL SOARES</t>
+          <t>OBRA PARA REFORMA E CONTENÇÃO E ESTABILIDADE DE TALUDE E DO PRÉDIO EE SÃO JOSÉ</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2585,16 +2583,16 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>ARAGUARI</t>
+          <t>ALÉM PARAÍBA</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380000</v>
+        <v>691600</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -2634,12 +2632,12 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA GERAL E RESTAURAÇÃO EE AFONSO PENA</t>
+          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE RAUL SOARES</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2653,16 +2651,16 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ARAGUARI</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>1194340</v>
+        <v>380000</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -2702,12 +2700,12 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE FRANCISCO SALES</t>
+          <t>OBRA PARA REFORMA GERAL E RESTAURAÇÃO EE AFONSO PENA</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2730,7 +2728,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>407740</v>
+        <v>1194340</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -2770,7 +2768,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO COMPLEMENTARES - UNIDADE I EE GOV MILTON CAMPOS</t>
+          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE FRANCISCO SALES</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2798,7 +2796,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>1102000</v>
+        <v>407740</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -2838,7 +2836,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>OBRA PARA TALUDE E MURO EE PROFA MARIA AMÉLIA GUIMARÃES</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO COMPLEMENTARES - UNIDADE I EE GOV MILTON CAMPOS</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2866,7 +2864,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>190000</v>
+        <v>1102000</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -2906,7 +2904,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO, CONSERVAÇÃO E PRESERVAÇÃO ANTIGA ESCOLA DE APRENDIZES MARINHEIROS E CASA DO COMANDANTE - FUCAM (EE PROFESSORA MARIETA AMORIM VIEIRA)</t>
+          <t>OBRA PARA TALUDE E MURO EE PROFA MARIA AMÉLIA GUIMARÃES</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2925,16 +2923,16 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BURITIZEIRO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>235600</v>
+        <v>190000</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -2974,7 +2972,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>ATENDIMENTOS ESCOLAS ESTADUAIS - CAIXAS ESCOLARES E CONVÊNIOS</t>
+          <t>RESTAURAÇÃO, CONSERVAÇÃO E PRESERVAÇÃO ANTIGA ESCOLA DE APRENDIZES MARINHEIROS E CASA DO COMANDANTE - FUCAM (EE PROFESSORA MARIETA AMORIM VIEIRA)</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2991,10 +2989,22 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Montes Claros</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>BURITIZEIRO</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>235600</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
@@ -3030,7 +3040,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS ESTRUTURAIS, ALÉM DE REFORMA E AMPLIAÇÃO DO PRÉDIO EE DR LAURO CORREA DO AMARAL</t>
+          <t>ATENDIMENTOS ESCOLAS ESTADUAIS - CAIXAS ESCOLARES E CONVÊNIOS</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3047,22 +3057,10 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Varginha</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>GUAPÉ</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>387600</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -3098,7 +3096,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>CONCLUSÃO DA OBRA DE CONTENÇÃO DE TALUDE E RECUPERAÇÕES NA CONSTRUÇÃO EE ANTÔNIO MARINHO CAMPOS</t>
+          <t>OBRA - PROBLEMAS ESTRUTURAIS, ALÉM DE REFORMA E AMPLIAÇÃO DO PRÉDIO EE DR LAURO CORREA DO AMARAL</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3117,16 +3115,16 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>GUAPÉ</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>361760</v>
+        <v>387600</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -3166,7 +3164,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>OBRA DE CONTENÇÃO, REFORMA E REFORÇO ESTRUTURAL DO PRÉDIO EE ANTÔNIO PAPINI</t>
+          <t>CONCLUSÃO DA OBRA DE CONTENÇÃO DE TALUDE E RECUPERAÇÕES NA CONSTRUÇÃO EE ANTÔNIO MARINHO CAMPOS</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3185,16 +3183,16 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>218500</v>
+        <v>361760</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -3234,7 +3232,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA/RESTAURAÇÃO E  REPAROS ESTRUTURAIS EE DUQUE DE CAXIAS</t>
+          <t>OBRA DE CONTENÇÃO, REFORMA E REFORÇO ESTRUTURAL DO PRÉDIO EE ANTÔNIO PAPINI</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3253,16 +3251,16 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>1976000</v>
+        <v>218500</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3302,7 +3300,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>OBRA DE CONSTRUÇÃO DA SEDESEDE DA SRE DE MONTES CLAROS</t>
+          <t>OBRA PARA REFORMA/RESTAURAÇÃO E  REPAROS ESTRUTURAIS EE DUQUE DE CAXIAS</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3321,16 +3319,16 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>805600</v>
+        <v>1976000</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -3370,7 +3368,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>OBRAS DE CONTENÇÃO EE AUGUSTO DE LIMA</t>
+          <t>OBRA DE CONSTRUÇÃO DA SEDESEDE DA SRE DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3389,16 +3387,16 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>760000</v>
+        <v>805600</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3438,7 +3436,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS  ESTRUTURAIS NO EDIFÍCIO, INCLUINDO INFILTRAÇÃO NAS PAREDES, DETERIORAÇÃO DO GUARDA-CORPO NA FACHADA, ABATIMENTO NO PISO, ASSOALHO DANIFICADO E INCLINAÇÃO DA FACHADA.EE PROFESSOR PINHEIRO CAMPOS</t>
+          <t>OBRAS DE CONTENÇÃO EE AUGUSTO DE LIMA</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3457,16 +3455,16 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>653600</v>
+        <v>760000</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -3506,12 +3504,12 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>REFORMA GERAL E RESTAURAÇÃO EE DOM PEDRO II</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS  ESTRUTURAIS NO EDIFÍCIO, INCLUINDO INFILTRAÇÃO NAS PAREDES, DETERIORAÇÃO DO GUARDA-CORPO NA FACHADA, ABATIMENTO NO PISO, ASSOALHO DANIFICADO E INCLINAÇÃO DA FACHADA.EE PROFESSOR PINHEIRO CAMPOS</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3525,16 +3523,16 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>1204600</v>
+        <v>653600</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -3574,12 +3572,12 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO EE PROFESSOR ANTÔNIO DIAS MACIEL</t>
+          <t>REFORMA GERAL E RESTAURAÇÃO EE DOM PEDRO II</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3593,16 +3591,16 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PATOS DE MINAS</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>1927740</v>
+        <v>1204600</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -3642,7 +3640,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>OBRA RESTAURAÇÃO INSTITUTO DE EDUCAÇÃO DE JUIZ DE FORA</t>
+          <t>OBRA PARA RESTAURAÇÃO EE PROFESSOR ANTÔNIO DIAS MACIEL</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3661,16 +3659,16 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>PATOS DE MINAS</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>653600</v>
+        <v>1927740</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -3710,7 +3708,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE HENRIQUE BURNIER</t>
+          <t>OBRA RESTAURAÇÃO INSTITUTO DE EDUCAÇÃO DE JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3738,7 +3736,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>19000</v>
+        <v>653600</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -3778,7 +3776,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE BATISTA DE OLIVEIRA</t>
+          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE HENRIQUE BURNIER</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3846,7 +3844,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>OBRA REFORMA, RESTAURAÇÃO E AMPLIAÇÃOEE ANA ROCHA (PREDIO EE FREI LEOPOLDO)</t>
+          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE BATISTA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3865,16 +3863,16 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>MATUTINA</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>1318600</v>
+        <v>19000</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -3914,12 +3912,12 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA DA EDIFICAÇÃO E EXECUÇÃO DAS OBRAS DE ESTABILIZAÇÃO DE TALUDE, REFORÇO DA CONTENÇÃO E CONSTRUÇÃO DE NOVO MURO DE DIVISA EE JULIETA DE OLIVEIRA MACEDO</t>
+          <t>OBRA REFORMA, RESTAURAÇÃO E AMPLIAÇÃOEE ANA ROCHA (PREDIO EE FREI LEOPOLDO)</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3933,16 +3931,16 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>MATUTINA</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>653600</v>
+        <v>1318600</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -3982,12 +3980,12 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE PRÉDIO DA SEDE DA SRE DE MURIAÉ</t>
+          <t>OBRA PARA REFORMA DA EDIFICAÇÃO E EXECUÇÃO DAS OBRAS DE ESTABILIZAÇÃO DE TALUDE, REFORÇO DA CONTENÇÃO E CONSTRUÇÃO DE NOVO MURO DE DIVISA EE JULIETA DE OLIVEIRA MACEDO</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -4010,7 +4008,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>19000</v>
+        <v>653600</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -4050,7 +4048,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA SEDE DA SRE DE NOVA ERA</t>
+          <t>CONSTRUÇÃO DE PRÉDIO DA SEDE DA SRE DE MURIAÉ</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4069,12 +4067,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q53" t="n">
@@ -4118,7 +4116,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>OBRAS PARA PROBLEMAS ESTRUTURAIS NO AUDITÓRIO (ESTRUTURA PISO E TELHADO) - REFORMA GERAL E RESTAURAÇÃO - PRÉDIO TOMBADOEE FRANCISCO FERNANDES</t>
+          <t>OBRA DE REFORMA SEDE DA SRE DE NOVA ERA</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4137,16 +4135,16 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>NOVA ERA</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>760000</v>
+        <v>19000</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -4186,7 +4184,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBRA PARA REFORMA GERAL / RESTAURAÇÃO EE CONSELHEIRO AFONSO PENA </t>
+          <t>OBRAS PARA PROBLEMAS ESTRUTURAIS NO AUDITÓRIO (ESTRUTURA PISO E TELHADO) - REFORMA GERAL E RESTAURAÇÃO - PRÉDIO TOMBADOEE FRANCISCO FERNANDES</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4205,16 +4203,16 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>PARAOPEBA</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>19000</v>
+        <v>760000</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -4254,7 +4252,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃOEE DOM LUSTOSA</t>
+          <t xml:space="preserve">OBRA PARA REFORMA GERAL / RESTAURAÇÃO EE CONSELHEIRO AFONSO PENA </t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4273,12 +4271,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PATROCÍNIO</t>
+          <t>PARAOPEBA</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -4322,7 +4320,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>OBRA DE RESTAURAÇÃOSEDE DA SRE DE PATROCÍNIO</t>
+          <t>OBRA PARA RESTAURAÇÃOEE DOM LUSTOSA</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4390,7 +4388,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO DO PRÉDIOEE FRANCISCA BOTELHO</t>
+          <t>OBRA DE RESTAURAÇÃOSEDE DA SRE DE PATROCÍNIO</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4409,16 +4407,16 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>PITANGUI</t>
+          <t>PATROCÍNIO</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>434720</v>
+        <v>19000</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -4458,7 +4456,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>OBRA  DE REFORMA E RESTAURAÇÃOCESEC TANCREDO NEVES (PRÉDIO OCUPADO ANTERIORMENTE PELA EE FARNESE MACIEL )</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO DO PRÉDIOEE FRANCISCA BOTELHO</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4477,16 +4475,16 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO</t>
+          <t>PITANGUI</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>221160</v>
+        <v>434720</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -4526,7 +4524,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>CONCLUSÃO DA OBRA DE REFORMA E RESTAURAÇÃO EE JOAO DOS SANTOS</t>
+          <t>OBRA  DE REFORMA E RESTAURAÇÃOCESEC TANCREDO NEVES (PRÉDIO OCUPADO ANTERIORMENTE PELA EE FARNESE MACIEL )</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4545,16 +4543,16 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>1748000</v>
+        <v>221160</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -4594,7 +4592,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISSEDE DA SRE DE SETE LAGOAS</t>
+          <t>CONCLUSÃO DA OBRA DE REFORMA E RESTAURAÇÃO EE JOAO DOS SANTOS</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4613,16 +4611,16 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479560</v>
+        <v>1748000</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -4662,7 +4660,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>OBRA PARA REPAROS ESTRUTURAIS (EXECUÇÃO DO REFORÇO DE FUNDAÇÃO E SERVIÇOS CORRELATOS) - 1A ETAPAEE DEPUTADO CARLOS PEIXOTO FILHO</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISSEDE DA SRE DE SETE LAGOAS</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4681,16 +4679,16 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>UBÁ</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>228000</v>
+        <v>479560</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -4730,12 +4728,12 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE ESCOLA - 16 SALAS DE AULA (NO BAIRRO JARDIM CÉLIA)EE 13 DE MAIO</t>
+          <t>OBRA PARA REPAROS ESTRUTURAIS (EXECUÇÃO DO REFORÇO DE FUNDAÇÃO E SERVIÇOS CORRELATOS) - 1A ETAPAEE DEPUTADO CARLOS PEIXOTO FILHO</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -4749,16 +4747,16 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>UBÁ</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>2552080</v>
+        <v>228000</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -4798,12 +4796,12 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>REFORMA / REFORÇO ESTRUTURALEE CORAÇÃO DE JESUS</t>
+          <t>CONSTRUÇÃO DE ESCOLA - 16 SALAS DE AULA (NO BAIRRO JARDIM CÉLIA)EE 13 DE MAIO</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4817,16 +4815,16 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>VARGINHA</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>1386240</v>
+        <v>2552080</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -4866,7 +4864,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA/RESTAURAÇÃO EE BRASIL</t>
+          <t>REFORMA / REFORÇO ESTRUTURALEE CORAÇÃO DE JESUS</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4894,7 +4892,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>1900000</v>
+        <v>1386240</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -4934,7 +4932,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA E RESTAURAÇÃOEE DR. JOÃO PINHEIRO</t>
+          <t>OBRA PARA REFORMA/RESTAURAÇÃO EE BRASIL</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4958,11 +4956,11 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ</t>
+          <t>VARGINHA</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>1008140</v>
+        <v>1900000</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -5002,7 +5000,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>OBRAS PARA MURO DE ARRIMO E DRENAGEM, ALÉM DE REFORMA/RESTAURAÇÃO EE MINISTRO EDMUNDO LINS</t>
+          <t>OBRA DE REFORMA E RESTAURAÇÃOEE DR. JOÃO PINHEIRO</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5021,16 +5019,16 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>SERRO</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>380000</v>
+        <v>1008140</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -5070,7 +5068,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃOEE DR. ARTHUR BERNARDES</t>
+          <t>OBRAS PARA MURO DE ARRIMO E DRENAGEM, ALÉM DE REFORMA/RESTAURAÇÃO EE MINISTRO EDMUNDO LINS</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5089,16 +5087,16 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>SERRO</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>228000</v>
+        <v>380000</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -5138,7 +5136,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISEE HAYDÉE DE SOUZA ABREU</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃOEE DR. ARTHUR BERNARDES</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5157,16 +5155,16 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539600</v>
+        <v>228000</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -5206,7 +5204,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>OBRA - MANUTENÇÃO E REVISÃO COMPLETA DAS COBERTURAS; PINTURA EXTERNA E INTERNA; RESTAURO DE ESQUADRIAS;  REVISÃO DE TODA A REDE ELÉTRICA; RESTAURO DA PINTURA ARTÍSTICA DO RODATETO E PROSPECÇÃO EXPLORATÓRIA NO HALL DE ENTRADA, VISANDO AVALIAR A EXISTÊ</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISEE HAYDÉE DE SOUZA ABREU</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5225,16 +5223,16 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>19000</v>
+        <v>539600</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -5274,12 +5272,12 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO EE AFONSO PENA</t>
+          <t>OBRA - MANUTENÇÃO E REVISÃO COMPLETA DAS COBERTURAS; PINTURA EXTERNA E INTERNA; RESTAURO DE ESQUADRIAS;  REVISÃO DE TODA A REDE ELÉTRICA; RESTAURO DA PINTURA ARTÍSTICA DO RODATETO E PROSPECÇÃO EXPLORATÓRIA NO HALL DE ENTRADA, VISANDO AVALIAR A EXISTÊ</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -5293,16 +5291,16 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>VARGINHA</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>2074800</v>
+        <v>19000</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -5316,35 +5314,33 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1301</v>
+        <v>1261</v>
       </c>
       <c r="B72" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C72" t="n">
-        <v>451</v>
+        <v>368</v>
       </c>
       <c r="D72" t="n">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="E72" t="n">
-        <v>1037</v>
+        <v>4519</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
         <v>71</v>
       </c>
-      <c r="I72" t="n">
-        <v>12404</v>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>DC-018/2023-Execução das serviço de Aumento de capacidade e Recuperação de Rodovia (aumento de capacidade) no trecho Três Pontas - Varginhas (Estaca 80 a 610), com 10,60 km de extensão, na Rodovia MG-167</t>
+          <t>OBRA PARA RESTAURAÇÃO EE AFONSO PENA</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5353,10 +5349,12 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5366,14 +5364,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>TRÊS PONTAS</t>
+          <t>VARGINHA</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>280106</v>
+        <v>2074800</v>
       </c>
       <c r="R72" t="n">
-        <v>519640</v>
+        <v>0</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -5408,11 +5406,11 @@
         <v>72</v>
       </c>
       <c r="I73" t="n">
-        <v>12780</v>
+        <v>12404</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Execução das obras de Implantação de Passarela na Rodovia MG-010, Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00 m</t>
+          <t>DC-018/2023-Execução das serviço de Aumento de capacidade e Recuperação de Rodovia (aumento de capacidade) no trecho Três Pontas - Varginhas (Estaca 80 a 610), com 10,60 km de extensão, na Rodovia MG-167</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5429,19 +5427,19 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>TRÊS PONTAS</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>894720</v>
+        <v>280106</v>
       </c>
       <c r="R73" t="n">
-        <v>4087644</v>
+        <v>519640</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -5476,11 +5474,11 @@
         <v>73</v>
       </c>
       <c r="I74" t="n">
-        <v>10397</v>
+        <v>12780</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>PRC-22.021/18 -Melhoramento e pavimentação no trecho Ibertioga  Piedade do Rio Grande, na Rodovia MG/338, extensão de 13,25km</t>
+          <t>Execução das obras de Implantação de Passarela na Rodovia MG-010, Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00 m</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5497,19 +5495,19 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>IBERTIOGA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>8264640</v>
+        <v>894720</v>
       </c>
       <c r="R74" t="n">
-        <v>19153735</v>
+        <v>4087644</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -5544,11 +5542,11 @@
         <v>74</v>
       </c>
       <c r="I75" t="n">
-        <v>12850</v>
+        <v>10397</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do trecho de Jaboticatubas - Lagoa Santa, em rodovia Municipal.</t>
+          <t>PRC-22.021/18 -Melhoramento e pavimentação no trecho Ibertioga  Piedade do Rio Grande, na Rodovia MG/338, extensão de 13,25km</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5565,19 +5563,19 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS</t>
+          <t>IBERTIOGA</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>3155040</v>
+        <v>8264640</v>
       </c>
       <c r="R75" t="n">
-        <v>23943007</v>
+        <v>19153735</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -5612,11 +5610,11 @@
         <v>75</v>
       </c>
       <c r="I76" t="n">
-        <v>12634</v>
+        <v>12850</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do Trecho Itapagipe - Entrº 364 (Campina Verde) MGC 154 - LOTE 01</t>
+          <t>Melhoramento e pavimentação do trecho de Jaboticatubas - Lagoa Santa, em rodovia Municipal.</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5633,19 +5631,19 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>ITAPAGIPE</t>
+          <t>JABOTICATUBAS</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>4840800</v>
+        <v>3155040</v>
       </c>
       <c r="R76" t="n">
-        <v>26593690</v>
+        <v>23943007</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -5680,11 +5678,11 @@
         <v>76</v>
       </c>
       <c r="I77" t="n">
-        <v>12785</v>
+        <v>12634</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Execução da Obra de Engenharia de Melhoramento e pavimentação da Interseção de acesso ao Presídio de Iturama, na via Municipal, com extensão de 2,000 km.</t>
+          <t>Melhoramento e pavimentação do Trecho Itapagipe - Entrº 364 (Campina Verde) MGC 154 - LOTE 01</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5706,14 +5704,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>ITURAMA</t>
+          <t>ITAPAGIPE</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>613500</v>
+        <v>4840800</v>
       </c>
       <c r="R77" t="n">
-        <v>2870210</v>
+        <v>26593690</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -5748,11 +5746,11 @@
         <v>77</v>
       </c>
       <c r="I78" t="n">
-        <v>12824</v>
+        <v>12785</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação em Rodovia de Ligação no trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700 km e Segmento 2 (835 a 1250), extensão 8,300 km.</t>
+          <t>Execução da Obra de Engenharia de Melhoramento e pavimentação da Interseção de acesso ao Presídio de Iturama, na via Municipal, com extensão de 2,000 km.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5769,19 +5767,19 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>PARACATU</t>
+          <t>ITURAMA</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>5963400</v>
+        <v>613500</v>
       </c>
       <c r="R78" t="n">
-        <v>23280000</v>
+        <v>2870210</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -5816,11 +5814,11 @@
         <v>78</v>
       </c>
       <c r="I79" t="n">
-        <v>4716</v>
+        <v>12824</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Entr. BR/365-Entr. LMG/782 (p/ Iraí de Minas), Monte Carmelo-Chapada de Minas e Pindaibas-Ent.BR/365</t>
+          <t>Melhoramento e Pavimentação em Rodovia de Ligação no trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700 km e Segmento 2 (835 a 1250), extensão 8,300 km.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5837,19 +5835,19 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>MONTE CARMELO</t>
+          <t>PARACATU</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>3620820</v>
+        <v>5963400</v>
       </c>
       <c r="R79" t="n">
-        <v>19100000</v>
+        <v>23280000</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
@@ -5883,15 +5881,17 @@
       <c r="H80" t="n">
         <v>79</v>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="n">
+        <v>4716</v>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Recapeamento de vias / pavimentação de trecho rodoviário / pavimentação e obra de arte especial no trecho viário; para melhoria da infraestrutura viária do Estado de Minas Gerais (8 propostas de novos convênios)</t>
+          <t>Entr. BR/365-Entr. LMG/782 (p/ Iraí de Minas), Monte Carmelo-Chapada de Minas e Pindaibas-Ent.BR/365</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -5903,19 +5903,19 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTE CARMELO</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3620820</v>
       </c>
       <c r="R80" t="n">
-        <v>11755000</v>
+        <v>19100000</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
@@ -5935,10 +5935,10 @@
         <v>451</v>
       </c>
       <c r="D81" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="E81" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -5949,17 +5949,15 @@
       <c r="H81" t="n">
         <v>80</v>
       </c>
-      <c r="I81" t="n">
-        <v>11140</v>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSTRUÇÃO DE 64 UNIDADES HABITACIONAIS PAC FNHIS </t>
+          <t>Recapeamento de vias / pavimentação de trecho rodoviário / pavimentação e obra de arte especial no trecho viário; para melhoria da infraestrutura viária do Estado de Minas Gerais (8 propostas de novos convênios)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -5971,19 +5969,19 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>1839798</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3269655</v>
+        <v>11755000</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
@@ -6018,11 +6016,11 @@
         <v>81</v>
       </c>
       <c r="I82" t="n">
-        <v>11531</v>
+        <v>11140</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL DO RIBEIRÃO ARRUDAS - FNHIS/2009 - Continuidade da execução do PTTS (Programa de Trabalho Técnico-Social)</t>
+          <t xml:space="preserve">CONSTRUÇÃO DE 64 UNIDADES HABITACIONAIS PAC FNHIS </t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6048,10 +6046,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>222899</v>
+        <v>1839798</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>3269655</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
@@ -6074,7 +6072,7 @@
         <v>99</v>
       </c>
       <c r="E83" t="n">
-        <v>4262</v>
+        <v>1038</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -6085,10 +6083,12 @@
       <c r="H83" t="n">
         <v>82</v>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>11531</v>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Aquisição de materiais para obras - mata-burros, vigas metálicas e bueiros metálicos</t>
+          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL DO RIBEIRÃO ARRUDAS - FNHIS/2009 - Continuidade da execução do PTTS (Programa de Trabalho Técnico-Social)</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6105,16 +6105,16 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>10932874</v>
+        <v>222899</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
@@ -6131,16 +6131,16 @@
         <v>1301</v>
       </c>
       <c r="B84" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C84" t="n">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D84" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="E84" t="n">
-        <v>4290</v>
+        <v>4262</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -6151,12 +6151,10 @@
       <c r="H84" t="n">
         <v>83</v>
       </c>
-      <c r="I84" t="n">
-        <v>12510</v>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
+          <t>Aquisição de materiais para obras - mata-burros, vigas metálicas e bueiros metálicos</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6173,19 +6171,19 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>10932874</v>
       </c>
       <c r="R84" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
@@ -6219,15 +6217,17 @@
       <c r="H85" t="n">
         <v>84</v>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>12510</v>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Brasília)</t>
+          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6248,10 +6248,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>478579</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>40000000</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
@@ -6288,7 +6288,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Civilização/Vilarinho)</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Brasília)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>2246479</v>
+        <v>478579</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE -  Obras Estações  BRT MG10)</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Civilização/Vilarinho)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>156926</v>
+        <v>2246479</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
@@ -6397,16 +6397,16 @@
         <v>1301</v>
       </c>
       <c r="B88" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C88" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D88" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E88" t="n">
-        <v>1036</v>
+        <v>4290</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -6417,17 +6417,15 @@
       <c r="H88" t="n">
         <v>87</v>
       </c>
-      <c r="I88" t="n">
-        <v>12453</v>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE -  Obras Estações  BRT MG10)</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -6439,19 +6437,19 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>ALÉM PARAÍBA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>156926</v>
       </c>
       <c r="R88" t="n">
-        <v>539924</v>
+        <v>0</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
@@ -6486,11 +6484,11 @@
         <v>88</v>
       </c>
       <c r="I89" t="n">
-        <v>12454</v>
+        <v>12453</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
+          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6512,14 +6510,14 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>ALÉM PARAÍBA</t>
         </is>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>15337533</v>
+        <v>539924</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
@@ -6554,11 +6552,11 @@
         <v>89</v>
       </c>
       <c r="I90" t="n">
-        <v>11521</v>
+        <v>12454</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6575,19 +6573,19 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>SABARÁ</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>1440021</v>
+        <v>15337533</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
@@ -6622,11 +6620,11 @@
         <v>90</v>
       </c>
       <c r="I91" t="n">
-        <v>11519</v>
+        <v>11521</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6643,19 +6641,19 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>SABARÁ</t>
         </is>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>6942767</v>
+        <v>1440021</v>
       </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
@@ -6690,16 +6688,16 @@
         <v>91</v>
       </c>
       <c r="I92" t="n">
-        <v>11512</v>
+        <v>11519</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
+          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -6716,14 +6714,14 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>14686005</v>
+        <v>6942767</v>
       </c>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
@@ -6758,16 +6756,16 @@
         <v>92</v>
       </c>
       <c r="I93" t="n">
-        <v>11514</v>
+        <v>11512</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
+          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -6779,19 +6777,19 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>52160376</v>
+        <v>14686005</v>
       </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
@@ -6826,11 +6824,11 @@
         <v>93</v>
       </c>
       <c r="I94" t="n">
-        <v>11511</v>
+        <v>11514</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
+          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6847,19 +6845,19 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>20521500</v>
+        <v>52160376</v>
       </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
@@ -6894,11 +6892,11 @@
         <v>94</v>
       </c>
       <c r="I95" t="n">
-        <v>11520</v>
+        <v>11511</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6915,19 +6913,19 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>SANTA LUZIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>6952445</v>
+        <v>20521500</v>
       </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
@@ -6962,11 +6960,11 @@
         <v>95</v>
       </c>
       <c r="I96" t="n">
-        <v>11513</v>
+        <v>11520</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
+          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6983,19 +6981,19 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SANTA LUZIA</t>
         </is>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>12959175</v>
+        <v>6952445</v>
       </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
@@ -7030,11 +7028,11 @@
         <v>96</v>
       </c>
       <c r="I97" t="n">
-        <v>11977</v>
+        <v>11513</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7051,19 +7049,19 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>CATAGUASES</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>38244490</v>
+        <v>12959175</v>
       </c>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
@@ -7098,11 +7096,11 @@
         <v>97</v>
       </c>
       <c r="I98" t="n">
-        <v>11162</v>
+        <v>11977</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>OBRAS DE ESTABILIZAÇÃO E CONTENÇÃO DE ENCOSTAS E DESLIZAMENTOS EM ÁREAS URBANAS</t>
+          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7119,19 +7117,19 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CATAGUASES</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>9858067</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>38244490</v>
       </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
@@ -7154,7 +7152,7 @@
         <v>139</v>
       </c>
       <c r="E99" t="n">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
@@ -7166,11 +7164,11 @@
         <v>98</v>
       </c>
       <c r="I99" t="n">
-        <v>12699</v>
+        <v>11162</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A CONCLUSÃO DA IMPLEMENTAÇÃO DO PTTS  PROJETO DE TRABALHO TÉCNICO SOCIAL- PROGRAMA DE REQUALIFICAÇÃO URBANA E AMBIENTAL E CONTROLE DE CHEIAS DO CÓRREGO FERRUGEM</t>
+          <t>OBRAS DE ESTABILIZAÇÃO E CONTENÇÃO DE ENCOSTAS E DESLIZAMENTOS EM ÁREAS URBANAS</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7187,16 +7185,16 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>299895</v>
+        <v>9858067</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
@@ -7234,11 +7232,11 @@
         <v>99</v>
       </c>
       <c r="I100" t="n">
-        <v>11536</v>
+        <v>12699</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Construção de 192 unidades habitacionais referente a 2ª etapa da Requalificação urbana e ambiental do Córrego Ferrugem</t>
+          <t>SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A CONCLUSÃO DA IMPLEMENTAÇÃO DO PTTS  PROJETO DE TRABALHO TÉCNICO SOCIAL- PROGRAMA DE REQUALIFICAÇÃO URBANA E AMBIENTAL E CONTROLE DE CHEIAS DO CÓRREGO FERRUGEM</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7264,7 +7262,7 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>4565604</v>
+        <v>299895</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
@@ -7290,7 +7288,7 @@
         <v>139</v>
       </c>
       <c r="E101" t="n">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -7302,11 +7300,11 @@
         <v>100</v>
       </c>
       <c r="I101" t="n">
-        <v>11855</v>
+        <v>11536</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>REMANESCENTE DAS OBRAS DE INFRAESTRUTURA PARA A CONCLUSAO DAS BACIAS DO CONTROLE DE CHEIAS DO CORREGO RIACHO DAS PEDRAS.</t>
+          <t>Construção de 192 unidades habitacionais referente a 2ª etapa da Requalificação urbana e ambiental do Córrego Ferrugem</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7332,10 +7330,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>6286532</v>
+        <v>4565604</v>
       </c>
       <c r="R101" t="n">
-        <v>2728583</v>
+        <v>0</v>
       </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
@@ -7370,11 +7368,11 @@
         <v>101</v>
       </c>
       <c r="I102" t="n">
-        <v>11973</v>
+        <v>11855</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>execução do Plano de Trabalho Técnico-Social - PTTS, que é uma exigência do contrato de financiamento PAC RIACHO</t>
+          <t>REMANESCENTE DAS OBRAS DE INFRAESTRUTURA PARA A CONCLUSAO DAS BACIAS DO CONTROLE DE CHEIAS DO CORREGO RIACHO DAS PEDRAS.</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -7400,10 +7398,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>193263</v>
+        <v>6286532</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2728583</v>
       </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
@@ -7414,19 +7412,19 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1371</v>
+        <v>1301</v>
       </c>
       <c r="B103" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C103" t="n">
-        <v>511</v>
+        <v>451</v>
       </c>
       <c r="D103" t="n">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="E103" t="n">
-        <v>4118</v>
+        <v>1041</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -7437,15 +7435,17 @@
       <c r="H103" t="n">
         <v>102</v>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="n">
+        <v>11973</v>
+      </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Programa Água Doce - RIMC</t>
+          <t>execução do Plano de Trabalho Técnico-Social - PTTS, que é uma exigência do contrato de financiamento PAC RIACHO</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -7457,19 +7457,19 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>193263</v>
       </c>
       <c r="R103" t="n">
-        <v>4547000</v>
+        <v>0</v>
       </c>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
@@ -7506,7 +7506,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Programa Água Doce - RITO</t>
+          <t>Programa Água Doce - RIMC</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q104" t="n">
@@ -7546,25 +7546,25 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1451</v>
+        <v>1371</v>
       </c>
       <c r="B105" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C105" t="n">
-        <v>421</v>
+        <v>511</v>
       </c>
       <c r="D105" t="n">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="E105" t="n">
-        <v>1048</v>
+        <v>4118</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
         <v>104</v>
@@ -7572,12 +7572,12 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
+          <t>Programa Água Doce - RITO</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -7589,19 +7589,19 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>904245</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>44308050</v>
+        <v>4547000</v>
       </c>
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
@@ -7618,13 +7618,13 @@
         <v>6</v>
       </c>
       <c r="C106" t="n">
-        <v>243</v>
+        <v>421</v>
       </c>
       <c r="D106" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E106" t="n">
-        <v>4441</v>
+        <v>1048</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
@@ -7638,7 +7638,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7655,19 +7655,19 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>6999284</v>
+        <v>904245</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>44308050</v>
       </c>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
@@ -7726,11 +7726,11 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>651694</v>
+        <v>6999284</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>ALFENAS</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q108" t="n">
@@ -7853,16 +7853,16 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>ALFENAS</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>1472757</v>
+        <v>651694</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
@@ -7919,16 +7919,16 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>651694</v>
+        <v>1472757</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
@@ -7985,16 +7985,16 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>18572878</v>
+        <v>651694</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
@@ -8008,25 +8008,25 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B112" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C112" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D112" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E112" t="n">
-        <v>4476</v>
+        <v>4441</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" t="n">
         <v>111</v>
@@ -8034,12 +8034,12 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO`S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -8051,16 +8051,16 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>270000</v>
+        <v>18572878</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
@@ -8083,10 +8083,10 @@
         <v>122</v>
       </c>
       <c r="D113" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E113" t="n">
-        <v>4465</v>
+        <v>4476</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
@@ -8100,7 +8100,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
+          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO`S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -8126,7 +8126,7 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>1100000</v>
+        <v>270000</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
@@ -8166,7 +8166,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
+          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>624000</v>
+        <v>1100000</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -8232,7 +8232,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
+          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>210000</v>
+        <v>624000</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
@@ -8298,7 +8298,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
+          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>150000</v>
+        <v>210000</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
@@ -8364,7 +8364,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
+          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>3918408</v>
+        <v>150000</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
@@ -8413,10 +8413,10 @@
         <v>122</v>
       </c>
       <c r="D118" t="n">
-        <v>705</v>
+        <v>156</v>
       </c>
       <c r="E118" t="n">
-        <v>2500</v>
+        <v>4465</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -8430,7 +8430,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
+          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8438,17 +8438,11 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M118" t="n">
-        <v>1</v>
-      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -8462,7 +8456,7 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>282000</v>
+        <v>3918408</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
@@ -8476,19 +8470,19 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="B119" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C119" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="D119" t="n">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="E119" t="n">
-        <v>1006</v>
+        <v>2500</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -8502,7 +8496,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
+          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -8510,28 +8504,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M119" t="n">
+        <v>1</v>
+      </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>282000</v>
       </c>
       <c r="R119" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
@@ -8554,7 +8554,7 @@
         <v>32</v>
       </c>
       <c r="E120" t="n">
-        <v>4063</v>
+        <v>1006</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
@@ -8568,7 +8568,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
+          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8585,19 +8585,19 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>19850000</v>
+        <v>1000000</v>
       </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
@@ -8608,19 +8608,19 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1541</v>
+        <v>1511</v>
       </c>
       <c r="B121" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C121" t="n">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="D121" t="n">
-        <v>705</v>
+        <v>32</v>
       </c>
       <c r="E121" t="n">
-        <v>2500</v>
+        <v>4063</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
@@ -8634,12 +8634,12 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
+          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -8656,14 +8656,14 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>2896100</v>
+        <v>150000</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>19850000</v>
       </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
@@ -8674,19 +8674,19 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2011</v>
+        <v>1541</v>
       </c>
       <c r="B122" t="n">
         <v>10</v>
       </c>
       <c r="C122" t="n">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="D122" t="n">
-        <v>88</v>
+        <v>705</v>
       </c>
       <c r="E122" t="n">
-        <v>4231</v>
+        <v>2500</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
@@ -8697,17 +8697,15 @@
       <c r="H122" t="n">
         <v>121</v>
       </c>
-      <c r="I122" t="n">
-        <v>12871</v>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
+          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -8728,10 +8726,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>2896100</v>
       </c>
       <c r="R122" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
@@ -8766,11 +8764,11 @@
         <v>122</v>
       </c>
       <c r="I123" t="n">
-        <v>9999</v>
+        <v>12871</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
+          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8799,7 +8797,7 @@
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>1600000</v>
+        <v>2000000</v>
       </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
@@ -8816,13 +8814,13 @@
         <v>10</v>
       </c>
       <c r="C124" t="n">
-        <v>122</v>
+        <v>302</v>
       </c>
       <c r="D124" t="n">
-        <v>705</v>
+        <v>88</v>
       </c>
       <c r="E124" t="n">
-        <v>2500</v>
+        <v>4231</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
@@ -8834,11 +8832,11 @@
         <v>123</v>
       </c>
       <c r="I124" t="n">
-        <v>12690</v>
+        <v>9999</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
+          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8867,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>2200000</v>
+        <v>1600000</v>
       </c>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
@@ -8878,19 +8876,19 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2101</v>
+        <v>2011</v>
       </c>
       <c r="B125" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C125" t="n">
-        <v>541</v>
+        <v>122</v>
       </c>
       <c r="D125" t="n">
-        <v>31</v>
+        <v>705</v>
       </c>
       <c r="E125" t="n">
-        <v>4058</v>
+        <v>2500</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
@@ -8901,10 +8899,12 @@
       <c r="H125" t="n">
         <v>124</v>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="n">
+        <v>12690</v>
+      </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Construção do Cetras de Governador Valadares</t>
+          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8912,34 +8912,28 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M125" t="n">
-        <v>1</v>
-      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>2200000</v>
       </c>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
@@ -8962,7 +8956,7 @@
         <v>31</v>
       </c>
       <c r="E126" t="n">
-        <v>4059</v>
+        <v>4058</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
@@ -8976,7 +8970,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>APA Parque Cataguás</t>
+          <t>Construção do Cetras de Governador Valadares</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -9008,7 +9002,7 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>1000000</v>
+        <v>350000</v>
       </c>
       <c r="R126" t="n">
         <v>0</v>
@@ -9022,19 +9016,19 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2151</v>
+        <v>2101</v>
       </c>
       <c r="B127" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C127" t="n">
-        <v>572</v>
+        <v>541</v>
       </c>
       <c r="D127" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="E127" t="n">
-        <v>1023</v>
+        <v>4059</v>
       </c>
       <c r="F127" t="n">
         <v>1</v>
@@ -9048,7 +9042,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
+          <t>APA Parque Cataguás</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -9056,25 +9050,31 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M127" t="n">
+        <v>1</v>
+      </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
@@ -9094,13 +9094,13 @@
         <v>12</v>
       </c>
       <c r="C128" t="n">
-        <v>122</v>
+        <v>572</v>
       </c>
       <c r="D128" t="n">
-        <v>705</v>
+        <v>75</v>
       </c>
       <c r="E128" t="n">
-        <v>2500</v>
+        <v>1023</v>
       </c>
       <c r="F128" t="n">
         <v>1</v>
@@ -9114,7 +9114,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
@@ -9154,19 +9154,19 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2161</v>
+        <v>2151</v>
       </c>
       <c r="B129" t="n">
         <v>12</v>
       </c>
       <c r="C129" t="n">
-        <v>242</v>
+        <v>122</v>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>705</v>
       </c>
       <c r="E129" t="n">
-        <v>1030</v>
+        <v>2500</v>
       </c>
       <c r="F129" t="n">
         <v>1</v>
@@ -9180,12 +9180,12 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Projeto para melhoria de acessibilidade nas unidades da FUCAM</t>
+          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -9197,16 +9197,16 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>14000</v>
+        <v>1500000</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
@@ -9263,16 +9263,16 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>3000</v>
+        <v>14000</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
@@ -9329,12 +9329,12 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>ESMERALDAS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
         </is>
       </c>
       <c r="Q131" t="n">
@@ -9352,19 +9352,19 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2261</v>
+        <v>2161</v>
       </c>
       <c r="B132" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C132" t="n">
-        <v>303</v>
+        <v>242</v>
       </c>
       <c r="D132" t="n">
-        <v>154</v>
+        <v>5</v>
       </c>
       <c r="E132" t="n">
-        <v>4460</v>
+        <v>1030</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -9375,17 +9375,15 @@
       <c r="H132" t="n">
         <v>131</v>
       </c>
-      <c r="I132" t="n">
-        <v>12502</v>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Execução de Obras da nova sede da Divisão de Controle de Qualidade.</t>
+          <t>Projeto para melhoria de acessibilidade nas unidades da FUCAM</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -9402,11 +9400,11 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ESMERALDAS</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500000</v>
+        <v>3000</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
@@ -9426,13 +9424,13 @@
         <v>10</v>
       </c>
       <c r="C133" t="n">
-        <v>122</v>
+        <v>303</v>
       </c>
       <c r="D133" t="n">
-        <v>705</v>
+        <v>154</v>
       </c>
       <c r="E133" t="n">
-        <v>2500</v>
+        <v>4460</v>
       </c>
       <c r="F133" t="n">
         <v>1</v>
@@ -9444,11 +9442,11 @@
         <v>132</v>
       </c>
       <c r="I133" t="n">
-        <v>12500</v>
+        <v>12502</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Novo Prédio Administrativo da FUNED em Steel Frame (Unidade IV)</t>
+          <t>Execução de Obras da nova sede da Divisão de Controle de Qualidade.</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -9474,7 +9472,7 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>10535000</v>
+        <v>500000</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
@@ -9511,10 +9509,12 @@
       <c r="H134" t="n">
         <v>133</v>
       </c>
-      <c r="I134" t="inlineStr"/>
+      <c r="I134" t="n">
+        <v>12500</v>
+      </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Obras de adequação estrutural do refeitório para atendimento às exigências da Vigilância Sanitária Municipal.</t>
+          <t>Novo Prédio Administrativo da FUNED em Steel Frame (Unidade IV)</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500000</v>
+        <v>10535000</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -9554,19 +9554,19 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2301</v>
+        <v>2261</v>
       </c>
       <c r="B135" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C135" t="n">
-        <v>782</v>
+        <v>122</v>
       </c>
       <c r="D135" t="n">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="E135" t="n">
-        <v>4268</v>
+        <v>2500</v>
       </c>
       <c r="F135" t="n">
         <v>1</v>
@@ -9580,7 +9580,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MG-010 (CONCEIÇÃO DO MATO DENTRO A SERRO)</t>
+          <t>Obras de adequação estrutural do refeitório para atendimento às exigências da Vigilância Sanitária Municipal.</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -9597,19 +9597,19 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="R135" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr"/>
@@ -9646,7 +9646,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MG-129 (OURO PRETO A OURO BRANCO)</t>
+          <t>REABILITAÇÃO DA MG-010 (CONCEIÇÃO DO MATO DENTRO A SERRO)</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -9712,7 +9712,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO) E RECOMPOSIÇÃO DE TALUDE ERODIDO</t>
+          <t>REABILITAÇÃO DA MG-129 (OURO PRETO A OURO BRANCO)</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -9741,7 +9741,7 @@
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr"/>
@@ -9778,7 +9778,7 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
+          <t>RESTAURAÇÃO RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO) E RECOMPOSIÇÃO DE TALUDE ERODIDO</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9804,10 +9804,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>9792000</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
@@ -9844,7 +9844,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
+          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9870,7 +9870,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>1000000</v>
+        <v>9792000</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
+          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9936,7 +9936,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>143000</v>
+        <v>1000000</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
@@ -9976,7 +9976,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
+          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -10002,7 +10002,7 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>5876140</v>
+        <v>143000</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
@@ -10042,7 +10042,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -10068,7 +10068,7 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>1132500</v>
+        <v>5876140</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
@@ -10108,7 +10108,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>1000000</v>
+        <v>1132500</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
@@ -10174,7 +10174,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
+          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -10200,7 +10200,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>34710000</v>
+        <v>1000000</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
@@ -10240,7 +10240,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -10266,7 +10266,7 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>59000000</v>
+        <v>34710000</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
@@ -10306,7 +10306,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -10332,7 +10332,7 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>1000000</v>
+        <v>59000000</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
@@ -10372,7 +10372,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -10438,7 +10438,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -10464,7 +10464,7 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
@@ -10504,7 +10504,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
+          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -10530,7 +10530,7 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
@@ -10570,7 +10570,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>30980000</v>
+        <v>1000000</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
@@ -10636,7 +10636,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -10662,7 +10662,7 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>25655000</v>
+        <v>30980000</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
@@ -10702,7 +10702,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>66560000</v>
+        <v>25655000</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
@@ -10768,7 +10768,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
+          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -10794,7 +10794,7 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>1000000</v>
+        <v>66560000</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
@@ -10834,7 +10834,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
+          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -10860,7 +10860,7 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>25464500</v>
+        <v>1000000</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
@@ -10886,7 +10886,7 @@
         <v>81</v>
       </c>
       <c r="E155" t="n">
-        <v>4272</v>
+        <v>4268</v>
       </c>
       <c r="F155" t="n">
         <v>1</v>
@@ -10900,7 +10900,7 @@
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10926,7 +10926,7 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>100000</v>
+        <v>25464500</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
+          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -10992,7 +10992,7 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>24000000</v>
+        <v>100000</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
@@ -11032,7 +11032,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
+          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>252000</v>
+        <v>24000000</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
@@ -11098,7 +11098,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>319200</v>
+        <v>252000</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
@@ -11164,7 +11164,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>495600</v>
+        <v>319200</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
@@ -11230,7 +11230,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>679000</v>
+        <v>495600</v>
       </c>
       <c r="R160" t="n">
         <v>0</v>
@@ -11296,7 +11296,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440000</v>
+        <v>679000</v>
       </c>
       <c r="R161" t="n">
         <v>0</v>
@@ -11362,7 +11362,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -11388,7 +11388,7 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>14920000</v>
+        <v>440000</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
@@ -11428,7 +11428,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -11454,7 +11454,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>8798400</v>
+        <v>14920000</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
@@ -11494,7 +11494,7 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -11520,7 +11520,7 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>369600</v>
+        <v>8798400</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
@@ -11560,7 +11560,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
+          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -11586,7 +11586,7 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>1000000</v>
+        <v>369600</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
@@ -11626,7 +11626,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
+          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -11652,7 +11652,7 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>1203643</v>
+        <v>1000000</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
@@ -11692,7 +11692,7 @@
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
+          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -11718,7 +11718,7 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>730000</v>
+        <v>1203643</v>
       </c>
       <c r="R167" t="n">
         <v>0</v>
@@ -11758,7 +11758,7 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
+          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>66619</v>
+        <v>730000</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
+          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -11850,7 +11850,7 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>901000</v>
+        <v>66619</v>
       </c>
       <c r="R169" t="n">
         <v>0</v>
@@ -11890,7 +11890,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11916,7 +11916,7 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>100000</v>
+        <v>901000</v>
       </c>
       <c r="R170" t="n">
         <v>0</v>
@@ -11956,7 +11956,7 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -11982,7 +11982,7 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>170000</v>
+        <v>100000</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
@@ -12022,7 +12022,7 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
+          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -12048,7 +12048,7 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>2940000</v>
+        <v>170000</v>
       </c>
       <c r="R172" t="n">
         <v>0</v>
@@ -12088,7 +12088,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>810000</v>
+        <v>2940000</v>
       </c>
       <c r="R173" t="n">
         <v>0</v>
@@ -12154,7 +12154,7 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
+          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>542000</v>
+        <v>810000</v>
       </c>
       <c r="R174" t="n">
         <v>0</v>
@@ -12220,7 +12220,7 @@
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
+          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -12246,7 +12246,7 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>2163814</v>
+        <v>542000</v>
       </c>
       <c r="R175" t="n">
         <v>0</v>
@@ -12286,7 +12286,7 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
+          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -12312,7 +12312,7 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>25000000</v>
+        <v>2163814</v>
       </c>
       <c r="R176" t="n">
         <v>0</v>
@@ -12352,7 +12352,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
+          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500000</v>
+        <v>25000000</v>
       </c>
       <c r="R177" t="n">
         <v>0</v>
@@ -12418,7 +12418,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
+          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -12444,7 +12444,7 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>1382535</v>
+        <v>500000</v>
       </c>
       <c r="R178" t="n">
         <v>0</v>
@@ -12484,7 +12484,7 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -12510,7 +12510,7 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>1000000</v>
+        <v>1382535</v>
       </c>
       <c r="R179" t="n">
         <v>0</v>
@@ -12550,7 +12550,7 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -12576,7 +12576,7 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="R180" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
+          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -12642,7 +12642,7 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>168000</v>
+        <v>900000</v>
       </c>
       <c r="R181" t="n">
         <v>0</v>
@@ -12682,7 +12682,7 @@
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
+          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>249000</v>
+        <v>168000</v>
       </c>
       <c r="R182" t="n">
         <v>0</v>
@@ -12748,7 +12748,7 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
+          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -12774,7 +12774,7 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>705000</v>
+        <v>249000</v>
       </c>
       <c r="R183" t="n">
         <v>0</v>
@@ -12814,7 +12814,7 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
+          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -12840,7 +12840,7 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>58800</v>
+        <v>705000</v>
       </c>
       <c r="R184" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
+          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -12906,7 +12906,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>725000</v>
+        <v>58800</v>
       </c>
       <c r="R185" t="n">
         <v>0</v>
@@ -12932,7 +12932,7 @@
         <v>81</v>
       </c>
       <c r="E186" t="n">
-        <v>4275</v>
+        <v>4272</v>
       </c>
       <c r="F186" t="n">
         <v>1</v>
@@ -12946,7 +12946,7 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
+          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -12972,10 +12972,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>725000</v>
       </c>
       <c r="R186" t="n">
-        <v>82286728</v>
+        <v>0</v>
       </c>
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr"/>
@@ -13012,7 +13012,7 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
+          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -13041,7 +13041,7 @@
         <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>22137718</v>
+        <v>82286728</v>
       </c>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
@@ -13078,7 +13078,7 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
+          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -13107,7 +13107,7 @@
         <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>21757581</v>
+        <v>22137718</v>
       </c>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
@@ -13144,7 +13144,7 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
+          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -13173,7 +13173,7 @@
         <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>8036364</v>
+        <v>21757581</v>
       </c>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
@@ -13210,7 +13210,7 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
+          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -13239,7 +13239,7 @@
         <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>14063636</v>
+        <v>8036364</v>
       </c>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
@@ -13276,7 +13276,7 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
+          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -13305,7 +13305,7 @@
         <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>8100000</v>
+        <v>14063636</v>
       </c>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
@@ -13342,7 +13342,7 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
+          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -13371,7 +13371,7 @@
         <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>4804860</v>
+        <v>8100000</v>
       </c>
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr"/>
@@ -13408,7 +13408,7 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -13437,7 +13437,7 @@
         <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>6000001</v>
+        <v>4804860</v>
       </c>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
@@ -13474,7 +13474,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
+          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>11326937</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>6000001</v>
       </c>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
@@ -13540,7 +13540,7 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>19000000</v>
+        <v>11326937</v>
       </c>
       <c r="R195" t="n">
         <v>0</v>
@@ -13606,7 +13606,7 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13632,7 +13632,7 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>74941120</v>
+        <v>19000000</v>
       </c>
       <c r="R196" t="n">
         <v>0</v>
@@ -13672,7 +13672,7 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
+          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13698,7 +13698,7 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>38460000</v>
+        <v>74941120</v>
       </c>
       <c r="R197" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
+          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13764,7 +13764,7 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>1000000</v>
+        <v>38460000</v>
       </c>
       <c r="R198" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
-          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
+          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="R199" t="n">
         <v>0</v>
@@ -13870,7 +13870,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
+          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -13896,7 +13896,7 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="R200" t="n">
         <v>0</v>
@@ -13936,7 +13936,7 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
+          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -13962,7 +13962,7 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>6121131</v>
+        <v>1000000</v>
       </c>
       <c r="R201" t="n">
         <v>0</v>
@@ -14002,7 +14002,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
+          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>1000000</v>
+        <v>6121131</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
@@ -14068,7 +14068,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
+          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -14134,7 +14134,7 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -14200,7 +14200,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
+          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -14266,7 +14266,7 @@
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
-          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
+          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -14332,7 +14332,7 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
+          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -14398,7 +14398,7 @@
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
-          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
+          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>431808</v>
+        <v>1000000</v>
       </c>
       <c r="R208" t="n">
         <v>0</v>
@@ -14464,7 +14464,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
-          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
+          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>1000000</v>
+        <v>431808</v>
       </c>
       <c r="R209" t="n">
         <v>0</v>
@@ -14530,7 +14530,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
-          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
+          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -14596,7 +14596,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
+          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -14662,7 +14662,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
-          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
+          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14688,7 +14688,7 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>14356788</v>
+        <v>1000000</v>
       </c>
       <c r="R212" t="n">
         <v>0</v>
@@ -14728,7 +14728,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
+          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -14754,7 +14754,7 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>100000</v>
+        <v>14356788</v>
       </c>
       <c r="R213" t="n">
         <v>0</v>
@@ -14794,7 +14794,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
-          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
+          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14820,7 +14820,7 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="R214" t="n">
         <v>0</v>
@@ -14860,7 +14860,7 @@
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
-          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
+          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>35359852</v>
+        <v>1000000</v>
       </c>
       <c r="R215" t="n">
         <v>0</v>
@@ -14926,7 +14926,7 @@
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
-          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
+          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -14952,7 +14952,7 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>29030000</v>
+        <v>35359852</v>
       </c>
       <c r="R216" t="n">
         <v>0</v>
@@ -14992,7 +14992,7 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
-          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
+          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -15018,7 +15018,7 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>1000000</v>
+        <v>29030000</v>
       </c>
       <c r="R217" t="n">
         <v>0</v>
@@ -15058,7 +15058,7 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
+          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>3541727</v>
+        <v>1000000</v>
       </c>
       <c r="R218" t="n">
         <v>0</v>
@@ -15124,7 +15124,7 @@
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
-          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
+          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -15150,7 +15150,7 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>31280000</v>
+        <v>3541727</v>
       </c>
       <c r="R219" t="n">
         <v>0</v>
@@ -15176,7 +15176,7 @@
         <v>81</v>
       </c>
       <c r="E220" t="n">
-        <v>4287</v>
+        <v>4275</v>
       </c>
       <c r="F220" t="n">
         <v>1</v>
@@ -15190,7 +15190,7 @@
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
+          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -15216,7 +15216,7 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>1000</v>
+        <v>31280000</v>
       </c>
       <c r="R220" t="n">
         <v>0</v>
@@ -15242,7 +15242,7 @@
         <v>81</v>
       </c>
       <c r="E221" t="n">
-        <v>4289</v>
+        <v>4287</v>
       </c>
       <c r="F221" t="n">
         <v>1</v>
@@ -15256,7 +15256,7 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
+          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -15308,7 +15308,7 @@
         <v>81</v>
       </c>
       <c r="E222" t="n">
-        <v>4293</v>
+        <v>4289</v>
       </c>
       <c r="F222" t="n">
         <v>1</v>
@@ -15322,7 +15322,7 @@
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
-          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
+          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -15348,7 +15348,7 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>10000000</v>
+        <v>1000</v>
       </c>
       <c r="R222" t="n">
         <v>0</v>
@@ -15388,7 +15388,7 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
+          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -15414,7 +15414,7 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>1406178</v>
+        <v>10000000</v>
       </c>
       <c r="R223" t="n">
         <v>0</v>
@@ -15454,7 +15454,7 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
-          <t>04ª URG BARBACENA</t>
+          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>0</v>
+        <v>1406178</v>
       </c>
       <c r="R224" t="n">
-        <v>12870000</v>
+        <v>0</v>
       </c>
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr"/>
@@ -15520,7 +15520,7 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
-          <t>20ª URG FORMIGA</t>
+          <t>04ª URG BARBACENA</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -15586,7 +15586,7 @@
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
-          <t>28ª URG TEÓFILO OTONI</t>
+          <t>20ª URG FORMIGA</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -15615,7 +15615,7 @@
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>9575065</v>
+        <v>12870000</v>
       </c>
       <c r="S226" t="inlineStr"/>
       <c r="T226" t="inlineStr"/>
@@ -15652,7 +15652,7 @@
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
-          <t>30ª URG JUIZ DE FORA</t>
+          <t>28ª URG TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -15681,7 +15681,7 @@
         <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>12375000</v>
+        <v>9575065</v>
       </c>
       <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr"/>
@@ -15718,7 +15718,7 @@
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - SUL</t>
+          <t>30ª URG JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -15747,7 +15747,7 @@
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>14850000</v>
+        <v>12375000</v>
       </c>
       <c r="S228" t="inlineStr"/>
       <c r="T228" t="inlineStr"/>
@@ -15784,7 +15784,7 @@
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - NORTE</t>
+          <t>01ª URG BELO HORIZONTE - SUL</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -15850,7 +15850,7 @@
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
-          <t>31ª URG ITUIUTABA</t>
+          <t>01ª URG BELO HORIZONTE - NORTE</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -15879,7 +15879,7 @@
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>9900000</v>
+        <v>14850000</v>
       </c>
       <c r="S230" t="inlineStr"/>
       <c r="T230" t="inlineStr"/>
@@ -15916,7 +15916,7 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
+          <t>31ª URG ITUIUTABA</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -15942,10 +15942,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>654124898</v>
+        <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>9900000</v>
       </c>
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="inlineStr"/>
@@ -15982,7 +15982,7 @@
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
+          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -16008,7 +16008,7 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>30767861</v>
+        <v>654124898</v>
       </c>
       <c r="R232" t="n">
         <v>0</v>
@@ -16048,7 +16048,7 @@
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -16074,7 +16074,7 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>19976964</v>
+        <v>30767861</v>
       </c>
       <c r="R233" t="n">
         <v>0</v>
@@ -16114,7 +16114,7 @@
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
+          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>12895888</v>
+        <v>19976964</v>
       </c>
       <c r="R234" t="n">
         <v>0</v>
@@ -16180,7 +16180,7 @@
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -16206,7 +16206,7 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>11846334</v>
+        <v>12895888</v>
       </c>
       <c r="R235" t="n">
         <v>0</v>
@@ -16246,7 +16246,7 @@
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -16272,7 +16272,7 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>15201174</v>
+        <v>11846334</v>
       </c>
       <c r="R236" t="n">
         <v>0</v>
@@ -16312,7 +16312,7 @@
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -16338,7 +16338,7 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>12921920</v>
+        <v>15201174</v>
       </c>
       <c r="R237" t="n">
         <v>0</v>
@@ -16364,7 +16364,7 @@
         <v>81</v>
       </c>
       <c r="E238" t="n">
-        <v>4385</v>
+        <v>4293</v>
       </c>
       <c r="F238" t="n">
         <v>1</v>
@@ -16378,7 +16378,7 @@
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -16404,7 +16404,7 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>6382601</v>
+        <v>12921920</v>
       </c>
       <c r="R238" t="n">
         <v>0</v>
@@ -16444,7 +16444,7 @@
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
+          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -16470,7 +16470,7 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>30000000</v>
+        <v>6382601</v>
       </c>
       <c r="R239" t="n">
         <v>0</v>
@@ -16510,7 +16510,7 @@
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -16536,7 +16536,7 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>4000000</v>
+        <v>30000000</v>
       </c>
       <c r="R240" t="n">
         <v>0</v>
@@ -16559,10 +16559,10 @@
         <v>782</v>
       </c>
       <c r="D241" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E241" t="n">
-        <v>4280</v>
+        <v>4385</v>
       </c>
       <c r="F241" t="n">
         <v>1</v>
@@ -16576,7 +16576,7 @@
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -16642,7 +16642,7 @@
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
+          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -16668,7 +16668,7 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>470000</v>
+        <v>4000000</v>
       </c>
       <c r="R242" t="n">
         <v>0</v>
@@ -16708,7 +16708,7 @@
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
+          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>4000000</v>
+        <v>470000</v>
       </c>
       <c r="R243" t="n">
         <v>0</v>
@@ -16774,7 +16774,7 @@
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
+          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -16800,7 +16800,7 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
       <c r="R244" t="n">
         <v>0</v>
@@ -16840,7 +16840,7 @@
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
+          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -16866,7 +16866,7 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>420000</v>
+        <v>1000000</v>
       </c>
       <c r="R245" t="n">
         <v>0</v>
@@ -16906,7 +16906,7 @@
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
+          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -16932,7 +16932,7 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>790000</v>
+        <v>420000</v>
       </c>
       <c r="R246" t="n">
         <v>0</v>
@@ -16946,19 +16946,19 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="B247" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C247" t="n">
-        <v>363</v>
+        <v>782</v>
       </c>
       <c r="D247" t="n">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="E247" t="n">
-        <v>4006</v>
+        <v>4280</v>
       </c>
       <c r="F247" t="n">
         <v>1</v>
@@ -16972,39 +16972,33 @@
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
+          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
-        </is>
-      </c>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t>METRO QUADRADO</t>
-        </is>
-      </c>
-      <c r="M247" t="n">
-        <v>5000</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>UNAÍ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>5000000</v>
+        <v>790000</v>
       </c>
       <c r="R247" t="n">
         <v>0</v>
@@ -17018,19 +17012,19 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2321</v>
+        <v>2311</v>
       </c>
       <c r="B248" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C248" t="n">
-        <v>302</v>
+        <v>363</v>
       </c>
       <c r="D248" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="E248" t="n">
-        <v>4222</v>
+        <v>4006</v>
       </c>
       <c r="F248" t="n">
         <v>1</v>
@@ -17044,33 +17038,39 @@
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
+          <t>PARALISADO</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>METRO QUADRADO</t>
+        </is>
+      </c>
+      <c r="M248" t="n">
+        <v>5000</v>
+      </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>UNAÍ</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>800291</v>
+        <v>5000000</v>
       </c>
       <c r="R248" t="n">
         <v>0</v>
@@ -17132,11 +17132,11 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>174673</v>
+        <v>800291</v>
       </c>
       <c r="R249" t="n">
         <v>0</v>
@@ -17173,17 +17173,15 @@
       <c r="H250" t="n">
         <v>249</v>
       </c>
-      <c r="I250" t="n">
-        <v>11877</v>
-      </c>
+      <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L250" t="inlineStr"/>
@@ -17195,16 +17193,16 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>1088908</v>
+        <v>174673</v>
       </c>
       <c r="R250" t="n">
         <v>0</v>
@@ -17218,19 +17216,19 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2361</v>
+        <v>2321</v>
       </c>
       <c r="B251" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C251" t="n">
-        <v>846</v>
+        <v>302</v>
       </c>
       <c r="D251" t="n">
-        <v>705</v>
+        <v>87</v>
       </c>
       <c r="E251" t="n">
-        <v>7004</v>
+        <v>4222</v>
       </c>
       <c r="F251" t="n">
         <v>1</v>
@@ -17241,10 +17239,12 @@
       <c r="H251" t="n">
         <v>250</v>
       </c>
-      <c r="I251" t="inlineStr"/>
+      <c r="I251" t="n">
+        <v>11877</v>
+      </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>Contrato a obra de reforma e ampliação</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -17259,10 +17259,22 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O251" t="inlineStr"/>
-      <c r="P251" t="inlineStr"/>
-      <c r="Q251" t="inlineStr"/>
-      <c r="R251" t="inlineStr"/>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Barbacena</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>SÃO JOÃO DEL REI</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>1088908</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0</v>
+      </c>
       <c r="S251" t="inlineStr"/>
       <c r="T251" t="inlineStr"/>
       <c r="U251" t="inlineStr"/>
@@ -17275,16 +17287,16 @@
         <v>2361</v>
       </c>
       <c r="B252" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C252" t="n">
-        <v>274</v>
+        <v>846</v>
       </c>
       <c r="D252" t="n">
-        <v>766</v>
+        <v>705</v>
       </c>
       <c r="E252" t="n">
-        <v>2113</v>
+        <v>7004</v>
       </c>
       <c r="F252" t="n">
         <v>1</v>
@@ -17335,10 +17347,10 @@
         <v>274</v>
       </c>
       <c r="D253" t="n">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E253" t="n">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="F253" t="n">
         <v>1</v>
@@ -17352,7 +17364,7 @@
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Possível obras de adequação da sede.</t>
+          <t>Possível adequação da sede</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -17367,22 +17379,10 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O253" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P253" t="inlineStr">
-        <is>
-          <t>BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
-      <c r="R253" t="n">
-        <v>2754406</v>
-      </c>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr"/>
+      <c r="R253" t="inlineStr"/>
       <c r="S253" t="inlineStr"/>
       <c r="T253" t="inlineStr"/>
       <c r="U253" t="inlineStr"/>
@@ -17392,19 +17392,19 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>2371</v>
+        <v>2361</v>
       </c>
       <c r="B254" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C254" t="n">
-        <v>609</v>
+        <v>274</v>
       </c>
       <c r="D254" t="n">
-        <v>78</v>
+        <v>767</v>
       </c>
       <c r="E254" t="n">
-        <v>4238</v>
+        <v>2114</v>
       </c>
       <c r="F254" t="n">
         <v>1</v>
@@ -17418,7 +17418,7 @@
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
+          <t>Possível obras de adequação da sede.</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -17444,10 +17444,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>8311374</v>
+        <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>2754406</v>
       </c>
       <c r="S254" t="inlineStr"/>
       <c r="T254" t="inlineStr"/>
@@ -17458,19 +17458,19 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2421</v>
+        <v>2371</v>
       </c>
       <c r="B255" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C255" t="n">
-        <v>544</v>
+        <v>609</v>
       </c>
       <c r="D255" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="E255" t="n">
-        <v>1016</v>
+        <v>4238</v>
       </c>
       <c r="F255" t="n">
         <v>1</v>
@@ -17484,7 +17484,7 @@
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
+          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -17501,16 +17501,16 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>477508</v>
+        <v>8311374</v>
       </c>
       <c r="R255" t="n">
         <v>0</v>
@@ -17524,19 +17524,19 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>3051</v>
+        <v>2421</v>
       </c>
       <c r="B256" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C256" t="n">
-        <v>364</v>
+        <v>544</v>
       </c>
       <c r="D256" t="n">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="E256" t="n">
-        <v>4016</v>
+        <v>1016</v>
       </c>
       <c r="F256" t="n">
         <v>1</v>
@@ -17550,7 +17550,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
+          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -17567,16 +17567,16 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>4825656</v>
+        <v>477508</v>
       </c>
       <c r="R256" t="n">
         <v>0</v>
@@ -17616,7 +17616,7 @@
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
+          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -17642,7 +17642,7 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>12649000</v>
+        <v>4825656</v>
       </c>
       <c r="R257" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
+          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>3715000</v>
+        <v>12649000</v>
       </c>
       <c r="R258" t="n">
         <v>0</v>
@@ -17725,16 +17725,16 @@
         <v>3051</v>
       </c>
       <c r="B259" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C259" t="n">
-        <v>571</v>
+        <v>364</v>
       </c>
       <c r="D259" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E259" t="n">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="F259" t="n">
         <v>1</v>
@@ -17748,7 +17748,7 @@
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
+          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -17774,10 +17774,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>0</v>
+        <v>3715000</v>
       </c>
       <c r="R259" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="S259" t="inlineStr"/>
       <c r="T259" t="inlineStr"/>
@@ -17788,19 +17788,19 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B260" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C260" t="n">
-        <v>61</v>
+        <v>571</v>
       </c>
       <c r="D260" t="n">
-        <v>706</v>
+        <v>16</v>
       </c>
       <c r="E260" t="n">
-        <v>2091</v>
+        <v>4018</v>
       </c>
       <c r="F260" t="n">
         <v>1</v>
@@ -17811,47 +17811,39 @@
       <c r="H260" t="n">
         <v>259</v>
       </c>
-      <c r="I260" t="n">
-        <v>12054</v>
-      </c>
+      <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
+          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M260" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
       <c r="N260" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q260" t="n">
         <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>11016496</v>
+        <v>250000</v>
       </c>
       <c r="S260" t="inlineStr"/>
       <c r="T260" t="inlineStr"/>
@@ -17886,11 +17878,11 @@
         <v>260</v>
       </c>
       <c r="I261" t="n">
-        <v>12806</v>
+        <v>12054</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
+          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -17913,19 +17905,19 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>CAMPO BELO</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q261" t="n">
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>19994210</v>
+        <v>11016496</v>
       </c>
       <c r="S261" t="inlineStr"/>
       <c r="T261" t="inlineStr"/>
@@ -17960,11 +17952,11 @@
         <v>261</v>
       </c>
       <c r="I262" t="n">
-        <v>12638</v>
+        <v>12806</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
+          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -17987,19 +17979,19 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>CARANGOLA</t>
+          <t>CAMPO BELO</t>
         </is>
       </c>
       <c r="Q262" t="n">
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>12843388</v>
+        <v>19994210</v>
       </c>
       <c r="S262" t="inlineStr"/>
       <c r="T262" t="inlineStr"/>
@@ -18034,11 +18026,11 @@
         <v>262</v>
       </c>
       <c r="I263" t="n">
-        <v>12400</v>
+        <v>12638</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -18061,19 +18053,19 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>IPATINGA</t>
+          <t>CARANGOLA</t>
         </is>
       </c>
       <c r="Q263" t="n">
         <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>18849069</v>
+        <v>12843388</v>
       </c>
       <c r="S263" t="inlineStr"/>
       <c r="T263" t="inlineStr"/>
@@ -18108,11 +18100,11 @@
         <v>263</v>
       </c>
       <c r="I264" t="n">
-        <v>12288</v>
+        <v>12400</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
+          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -18135,19 +18127,19 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>MONTE BELO</t>
+          <t>IPATINGA</t>
         </is>
       </c>
       <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>1950000</v>
+        <v>18849069</v>
       </c>
       <c r="S264" t="inlineStr"/>
       <c r="T264" t="inlineStr"/>
@@ -18182,11 +18174,11 @@
         <v>264</v>
       </c>
       <c r="I265" t="n">
-        <v>12816</v>
+        <v>12288</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Pirapora/MG</t>
+          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -18209,19 +18201,19 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>PIRAPORA</t>
+          <t>MONTE BELO</t>
         </is>
       </c>
       <c r="Q265" t="n">
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>22776109</v>
+        <v>1950000</v>
       </c>
       <c r="S265" t="inlineStr"/>
       <c r="T265" t="inlineStr"/>
@@ -18256,11 +18248,11 @@
         <v>265</v>
       </c>
       <c r="I266" t="n">
-        <v>12781</v>
+        <v>12816</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Construção do novo fórum da Comarca de São Gonçalo do Sapucaí/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Pirapora/MG</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -18283,19 +18275,19 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ</t>
+          <t>PIRAPORA</t>
         </is>
       </c>
       <c r="Q266" t="n">
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>14670005</v>
+        <v>22776109</v>
       </c>
       <c r="S266" t="inlineStr"/>
       <c r="T266" t="inlineStr"/>
@@ -18330,11 +18322,11 @@
         <v>266</v>
       </c>
       <c r="I267" t="n">
-        <v>12799</v>
+        <v>12781</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construção do novo Fórum da Comarca de Timóteo/MG </t>
+          <t>Construção do novo fórum da Comarca de São Gonçalo do Sapucaí/MG</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -18357,19 +18349,19 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ</t>
         </is>
       </c>
       <c r="Q267" t="n">
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>19506288</v>
+        <v>14670005</v>
       </c>
       <c r="S267" t="inlineStr"/>
       <c r="T267" t="inlineStr"/>
@@ -18404,16 +18396,16 @@
         <v>267</v>
       </c>
       <c r="I268" t="n">
-        <v>12833</v>
+        <v>12799</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Rio Novo.</t>
+          <t xml:space="preserve">Construção do novo Fórum da Comarca de Timóteo/MG </t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -18431,19 +18423,19 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>RIO NOVO</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q268" t="n">
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>4976096</v>
+        <v>19506288</v>
       </c>
       <c r="S268" t="inlineStr"/>
       <c r="T268" t="inlineStr"/>
@@ -18478,11 +18470,11 @@
         <v>268</v>
       </c>
       <c r="I269" t="n">
-        <v>12629</v>
+        <v>12833</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Luz.</t>
+          <t>Obra de construção do novo Fórum da Comarca de Rio Novo.</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -18505,19 +18497,19 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>LUZ</t>
+          <t>RIO NOVO</t>
         </is>
       </c>
       <c r="Q269" t="n">
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>7654409</v>
+        <v>4976096</v>
       </c>
       <c r="S269" t="inlineStr"/>
       <c r="T269" t="inlineStr"/>
@@ -18552,16 +18544,16 @@
         <v>269</v>
       </c>
       <c r="I270" t="n">
-        <v>12607</v>
+        <v>12629</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Reforma e ampliação do Fórum da Comarca de Sete Lagoas/MG.</t>
+          <t>Obra de construção do novo Fórum da Comarca de Luz.</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -18579,19 +18571,19 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>LUZ</t>
         </is>
       </c>
       <c r="Q270" t="n">
         <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>32235085</v>
+        <v>7654409</v>
       </c>
       <c r="S270" t="inlineStr"/>
       <c r="T270" t="inlineStr"/>
@@ -18626,11 +18618,11 @@
         <v>270</v>
       </c>
       <c r="I271" t="n">
-        <v>12639</v>
+        <v>12607</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Três Pontas</t>
+          <t>Reforma e ampliação do Fórum da Comarca de Sete Lagoas/MG.</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -18653,19 +18645,19 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>TRÊS PONTAS</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q271" t="n">
         <v>0</v>
       </c>
       <c r="R271" t="n">
-        <v>9489687</v>
+        <v>32235085</v>
       </c>
       <c r="S271" t="inlineStr"/>
       <c r="T271" t="inlineStr"/>
@@ -18700,16 +18692,16 @@
         <v>271</v>
       </c>
       <c r="I272" t="n">
-        <v>11547</v>
+        <v>12639</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>RETOMADA DA OBRA DE CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE ITAJUBÁ/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Três Pontas</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -18727,19 +18719,19 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>ITAJUBÁ</t>
+          <t>TRÊS PONTAS</t>
         </is>
       </c>
       <c r="Q272" t="n">
         <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>9366263</v>
+        <v>9489687</v>
       </c>
       <c r="S272" t="inlineStr"/>
       <c r="T272" t="inlineStr"/>
@@ -18774,11 +18766,11 @@
         <v>272</v>
       </c>
       <c r="I273" t="n">
-        <v>12856</v>
+        <v>11547</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Retomada da obra de construção do novo Fórum da Comarca de Poços de Caldas.</t>
+          <t>RETOMADA DA OBRA DE CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE ITAJUBÁ/MG</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -18806,14 +18798,14 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>POÇOS DE CALDAS</t>
+          <t>ITAJUBÁ</t>
         </is>
       </c>
       <c r="Q273" t="n">
         <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>11009635</v>
+        <v>9366263</v>
       </c>
       <c r="S273" t="inlineStr"/>
       <c r="T273" t="inlineStr"/>
@@ -18848,11 +18840,11 @@
         <v>273</v>
       </c>
       <c r="I274" t="n">
-        <v>12344</v>
+        <v>12856</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
+          <t>Retomada da obra de construção do novo Fórum da Comarca de Poços de Caldas.</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -18880,14 +18872,14 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>CAMANDUCAIA</t>
+          <t>POÇOS DE CALDAS</t>
         </is>
       </c>
       <c r="Q274" t="n">
         <v>0</v>
       </c>
       <c r="R274" t="n">
-        <v>4627222</v>
+        <v>11009635</v>
       </c>
       <c r="S274" t="inlineStr"/>
       <c r="T274" t="inlineStr"/>
@@ -18921,10 +18913,12 @@
       <c r="H275" t="n">
         <v>274</v>
       </c>
-      <c r="I275" t="inlineStr"/>
+      <c r="I275" t="n">
+        <v>12344</v>
+      </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de São João do Paraíso</t>
+          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -18947,19 +18941,19 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DO PARAÍSO</t>
+          <t>CAMANDUCAIA</t>
         </is>
       </c>
       <c r="Q275" t="n">
         <v>0</v>
       </c>
       <c r="R275" t="n">
-        <v>7290196</v>
+        <v>4627222</v>
       </c>
       <c r="S275" t="inlineStr"/>
       <c r="T275" t="inlineStr"/>
@@ -18996,7 +18990,7 @@
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de Brasilândia de Minas</t>
+          <t>Obra de construção do novo Fórum da Comarca de São João do Paraíso</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -19019,19 +19013,19 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>BRASILÂNDIA DE MINAS</t>
+          <t>SÃO JOÃO DO PARAÍSO</t>
         </is>
       </c>
       <c r="Q276" t="n">
         <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>1373680</v>
+        <v>7290196</v>
       </c>
       <c r="S276" t="inlineStr"/>
       <c r="T276" t="inlineStr"/>
@@ -19068,7 +19062,7 @@
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de São Gonçalo do Abaeté</t>
+          <t>Implantação do Fórum Digital no município de Brasilândia de Minas</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -19096,7 +19090,7 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO ABAETÉ</t>
+          <t>BRASILÂNDIA DE MINAS</t>
         </is>
       </c>
       <c r="Q277" t="n">
@@ -19140,7 +19134,7 @@
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de Ponto Chique</t>
+          <t>Implantação do Fórum Digital no município de São Gonçalo do Abaeté</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -19163,19 +19157,19 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>PONTO CHIQUE</t>
+          <t>SÃO GONÇALO DO ABAETÉ</t>
         </is>
       </c>
       <c r="Q278" t="n">
         <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>1760000</v>
+        <v>1373680</v>
       </c>
       <c r="S278" t="inlineStr"/>
       <c r="T278" t="inlineStr"/>
@@ -19209,17 +19203,15 @@
       <c r="H279" t="n">
         <v>278</v>
       </c>
-      <c r="I279" t="n">
-        <v>12627</v>
-      </c>
+      <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
+          <t>Implantação do Fórum Digital no município de Ponto Chique</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -19237,19 +19229,19 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>PONTO CHIQUE</t>
         </is>
       </c>
       <c r="Q279" t="n">
         <v>0</v>
       </c>
       <c r="R279" t="n">
-        <v>38084213</v>
+        <v>1760000</v>
       </c>
       <c r="S279" t="inlineStr"/>
       <c r="T279" t="inlineStr"/>
@@ -19284,11 +19276,11 @@
         <v>279</v>
       </c>
       <c r="I280" t="n">
-        <v>12146</v>
+        <v>12627</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
+          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -19323,7 +19315,7 @@
         <v>0</v>
       </c>
       <c r="R280" t="n">
-        <v>135013067</v>
+        <v>38084213</v>
       </c>
       <c r="S280" t="inlineStr"/>
       <c r="T280" t="inlineStr"/>
@@ -19358,11 +19350,11 @@
         <v>280</v>
       </c>
       <c r="I281" t="n">
-        <v>12703</v>
+        <v>12146</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Cincão - Reforma parcial para adequações da estrutura física dos Armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente</t>
+          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -19397,7 +19389,7 @@
         <v>0</v>
       </c>
       <c r="R281" t="n">
-        <v>1052449</v>
+        <v>135013067</v>
       </c>
       <c r="S281" t="inlineStr"/>
       <c r="T281" t="inlineStr"/>
@@ -19431,15 +19423,17 @@
       <c r="H282" t="n">
         <v>281</v>
       </c>
-      <c r="I282" t="inlineStr"/>
+      <c r="I282" t="n">
+        <v>12703</v>
+      </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Monte Alegre de Minas</t>
+          <t>Cincão - Reforma parcial para adequações da estrutura física dos Armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -19457,19 +19451,19 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>MONTE ALEGRE DE MINAS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q282" t="n">
         <v>0</v>
       </c>
       <c r="R282" t="n">
-        <v>6139672</v>
+        <v>1052449</v>
       </c>
       <c r="S282" t="inlineStr"/>
       <c r="T282" t="inlineStr"/>
@@ -19480,19 +19474,19 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>5011</v>
+        <v>4031</v>
       </c>
       <c r="B283" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C283" t="n">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="D283" t="n">
-        <v>133</v>
+        <v>706</v>
       </c>
       <c r="E283" t="n">
-        <v>3017</v>
+        <v>2091</v>
       </c>
       <c r="F283" t="n">
         <v>1</v>
@@ -19506,7 +19500,7 @@
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr">
         <is>
-          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
+          <t>Obra de construção do novo Fórum da Comarca de Monte Alegre de Minas</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -19514,28 +19508,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr"/>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M283" t="n">
+        <v>1</v>
+      </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTE ALEGRE DE MINAS</t>
         </is>
       </c>
       <c r="Q283" t="n">
         <v>0</v>
       </c>
       <c r="R283" t="n">
-        <v>800000</v>
+        <v>6139672</v>
       </c>
       <c r="S283" t="inlineStr"/>
       <c r="T283" t="inlineStr"/>
@@ -19546,19 +19546,19 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>5031</v>
+        <v>5011</v>
       </c>
       <c r="B284" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C284" t="n">
-        <v>572</v>
+        <v>122</v>
       </c>
       <c r="D284" t="n">
         <v>133</v>
       </c>
       <c r="E284" t="n">
-        <v>3015</v>
+        <v>3017</v>
       </c>
       <c r="F284" t="n">
         <v>1</v>
@@ -19572,7 +19572,7 @@
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr">
         <is>
-          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
+          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -19601,7 +19601,7 @@
         <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>4782988</v>
+        <v>800000</v>
       </c>
       <c r="S284" t="inlineStr"/>
       <c r="T284" t="inlineStr"/>
@@ -19612,19 +19612,19 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>5141</v>
+        <v>5031</v>
       </c>
       <c r="B285" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C285" t="n">
-        <v>126</v>
+        <v>572</v>
       </c>
       <c r="D285" t="n">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="E285" t="n">
-        <v>6006</v>
+        <v>3015</v>
       </c>
       <c r="F285" t="n">
         <v>1</v>
@@ -19638,7 +19638,7 @@
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr">
         <is>
-          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
+          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -19667,7 +19667,7 @@
         <v>0</v>
       </c>
       <c r="R285" t="n">
-        <v>16317109</v>
+        <v>4782988</v>
       </c>
       <c r="S285" t="inlineStr"/>
       <c r="T285" t="inlineStr"/>
@@ -19678,19 +19678,19 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>5251</v>
+        <v>5141</v>
       </c>
       <c r="B286" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C286" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D286" t="n">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="E286" t="n">
-        <v>3018</v>
+        <v>6006</v>
       </c>
       <c r="F286" t="n">
         <v>1</v>
@@ -19704,12 +19704,12 @@
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Projeto de Expansão</t>
+          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L286" t="inlineStr"/>
@@ -19721,19 +19721,19 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q286" t="n">
         <v>0</v>
       </c>
       <c r="R286" t="n">
-        <v>457766318</v>
+        <v>16317109</v>
       </c>
       <c r="S286" t="inlineStr"/>
       <c r="T286" t="inlineStr"/>
@@ -19744,19 +19744,19 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>5391</v>
+        <v>5251</v>
       </c>
       <c r="B287" t="n">
         <v>25</v>
       </c>
       <c r="C287" t="n">
-        <v>752</v>
+        <v>121</v>
       </c>
       <c r="D287" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="E287" t="n">
-        <v>3004</v>
+        <v>3018</v>
       </c>
       <c r="F287" t="n">
         <v>1</v>
@@ -19770,12 +19770,12 @@
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>Projeto de Expansão</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L287" t="inlineStr"/>
@@ -19792,14 +19792,14 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q287" t="n">
         <v>0</v>
       </c>
       <c r="R287" t="n">
-        <v>92004926</v>
+        <v>457766318</v>
       </c>
       <c r="S287" t="inlineStr"/>
       <c r="T287" t="inlineStr"/>
@@ -19853,19 +19853,19 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q288" t="n">
         <v>0</v>
       </c>
       <c r="R288" t="n">
-        <v>10705994</v>
+        <v>92004926</v>
       </c>
       <c r="S288" t="inlineStr"/>
       <c r="T288" t="inlineStr"/>
@@ -19919,19 +19919,19 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q289" t="n">
         <v>0</v>
       </c>
       <c r="R289" t="n">
-        <v>10464844</v>
+        <v>10705994</v>
       </c>
       <c r="S289" t="inlineStr"/>
       <c r="T289" t="inlineStr"/>
@@ -19985,19 +19985,19 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q290" t="n">
         <v>0</v>
       </c>
       <c r="R290" t="n">
-        <v>2098278</v>
+        <v>10464844</v>
       </c>
       <c r="S290" t="inlineStr"/>
       <c r="T290" t="inlineStr"/>
@@ -20051,19 +20051,19 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q291" t="n">
         <v>0</v>
       </c>
       <c r="R291" t="n">
-        <v>96721858</v>
+        <v>2098278</v>
       </c>
       <c r="S291" t="inlineStr"/>
       <c r="T291" t="inlineStr"/>
@@ -20117,19 +20117,19 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q292" t="n">
         <v>0</v>
       </c>
       <c r="R292" t="n">
-        <v>16415074</v>
+        <v>96721858</v>
       </c>
       <c r="S292" t="inlineStr"/>
       <c r="T292" t="inlineStr"/>
@@ -20183,19 +20183,19 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q293" t="n">
         <v>0</v>
       </c>
       <c r="R293" t="n">
-        <v>1</v>
+        <v>16415074</v>
       </c>
       <c r="S293" t="inlineStr"/>
       <c r="T293" t="inlineStr"/>
@@ -20218,7 +20218,7 @@
         <v>92</v>
       </c>
       <c r="E294" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F294" t="n">
         <v>1</v>
@@ -20232,7 +20232,7 @@
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -20249,19 +20249,19 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q294" t="n">
         <v>0</v>
       </c>
       <c r="R294" t="n">
-        <v>126817302</v>
+        <v>1</v>
       </c>
       <c r="S294" t="inlineStr"/>
       <c r="T294" t="inlineStr"/>
@@ -20315,19 +20315,19 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q295" t="n">
         <v>0</v>
       </c>
       <c r="R295" t="n">
-        <v>16058991</v>
+        <v>126817302</v>
       </c>
       <c r="S295" t="inlineStr"/>
       <c r="T295" t="inlineStr"/>
@@ -20381,19 +20381,19 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q296" t="n">
         <v>0</v>
       </c>
       <c r="R296" t="n">
-        <v>65795530</v>
+        <v>16058991</v>
       </c>
       <c r="S296" t="inlineStr"/>
       <c r="T296" t="inlineStr"/>
@@ -20447,19 +20447,19 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q297" t="n">
         <v>0</v>
       </c>
       <c r="R297" t="n">
-        <v>44156794</v>
+        <v>65795530</v>
       </c>
       <c r="S297" t="inlineStr"/>
       <c r="T297" t="inlineStr"/>
@@ -20513,19 +20513,19 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q298" t="n">
         <v>0</v>
       </c>
       <c r="R298" t="n">
-        <v>140716908</v>
+        <v>44156794</v>
       </c>
       <c r="S298" t="inlineStr"/>
       <c r="T298" t="inlineStr"/>
@@ -20579,19 +20579,19 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q299" t="n">
         <v>0</v>
       </c>
       <c r="R299" t="n">
-        <v>8715687</v>
+        <v>140716908</v>
       </c>
       <c r="S299" t="inlineStr"/>
       <c r="T299" t="inlineStr"/>
@@ -20645,19 +20645,19 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q300" t="n">
         <v>0</v>
       </c>
       <c r="R300" t="n">
-        <v>24622611</v>
+        <v>8715687</v>
       </c>
       <c r="S300" t="inlineStr"/>
       <c r="T300" t="inlineStr"/>
@@ -20677,10 +20677,10 @@
         <v>752</v>
       </c>
       <c r="D301" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E301" t="n">
-        <v>3001</v>
+        <v>3005</v>
       </c>
       <c r="F301" t="n">
         <v>1</v>
@@ -20694,7 +20694,7 @@
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Expansão do Sistema de Geração</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -20711,19 +20711,19 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q301" t="n">
         <v>0</v>
       </c>
       <c r="R301" t="n">
-        <v>1</v>
+        <v>24622611</v>
       </c>
       <c r="S301" t="inlineStr"/>
       <c r="T301" t="inlineStr"/>
@@ -20732,6 +20732,72 @@
       <c r="W301" t="inlineStr"/>
       <c r="X301" t="inlineStr"/>
     </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B302" t="n">
+        <v>25</v>
+      </c>
+      <c r="C302" t="n">
+        <v>752</v>
+      </c>
+      <c r="D302" t="n">
+        <v>94</v>
+      </c>
+      <c r="E302" t="n">
+        <v>3001</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" t="n">
+        <v>301</v>
+      </c>
+      <c r="I302" t="inlineStr"/>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>Expansão do Sistema de Geração</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q302" t="n">
+        <v>0</v>
+      </c>
+      <c r="R302" t="n">
+        <v>1</v>
+      </c>
+      <c r="S302" t="inlineStr"/>
+      <c r="T302" t="inlineStr"/>
+      <c r="U302" t="inlineStr"/>
+      <c r="V302" t="inlineStr"/>
+      <c r="W302" t="inlineStr"/>
+      <c r="X302" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
